--- a/Financial Analysis/GE.xlsx
+++ b/Financial Analysis/GE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54229264-2AEC-4B7D-B6ED-E31BDF8781D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF30A8F-06BD-48C1-9DE6-354B518BD6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BC781BE9-3E96-4748-AFB4-8F94403DD9F3}"/>
   </bookViews>
@@ -824,14 +824,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="7">
-        <v>306.79000000000002</v>
+        <v>329.58</v>
       </c>
       <c r="E3" s="5">
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>46053</v>
+        <v>46072</v>
       </c>
       <c r="G3" s="5">
         <v>46140</v>
@@ -855,7 +855,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>321761.35200000001</v>
+        <v>345663.50399999996</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -897,7 +897,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>291075.35200000001</v>
+        <v>314977.50399999996</v>
       </c>
     </row>
   </sheetData>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AN39" s="7">
         <f>Main!D3</f>
-        <v>306.79000000000002</v>
+        <v>329.58</v>
       </c>
     </row>
     <row r="40" spans="2:40" x14ac:dyDescent="0.3">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="AN40" s="12">
         <f>AN38/AN39-1</f>
-        <v>-0.1532616701402717</v>
+        <v>-0.21181245155147133</v>
       </c>
     </row>
     <row r="41" spans="2:40" x14ac:dyDescent="0.3">
@@ -4931,11 +4931,11 @@
       </c>
       <c r="N47" s="17">
         <f>Main!$D$9/Model!N46</f>
-        <v>2.2361341947775584</v>
+        <v>2.4197581912744197</v>
       </c>
       <c r="AA47" s="17">
         <f>Main!$D$9/Model!AA46</f>
-        <v>2.2361341947775584</v>
+        <v>2.4197581912744197</v>
       </c>
     </row>
     <row r="48" spans="2:40" x14ac:dyDescent="0.3">
@@ -4944,11 +4944,11 @@
       </c>
       <c r="N48" s="11">
         <f>N46/Main!$D$9-1</f>
-        <v>-0.55279964756342548</v>
+        <v>-0.58673556572471908</v>
       </c>
       <c r="AA48" s="11">
         <f>AA46/Main!$D$9-1</f>
-        <v>-0.55279964756342548</v>
+        <v>-0.58673556572471908</v>
       </c>
     </row>
   </sheetData>
